--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M212"/>
+  <dimension ref="A1:M213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12290.31</v>
+        <v>12227.16</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>30458.56</v>
+        <v>30302.06</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1068.72</v>
+        <v>1058.06</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14782.56</v>
+        <v>14635.02</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1212.03</v>
+        <v>1199.93</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10855.43</v>
+        <v>10734.49</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20696.59</v>
+        <v>20583.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>57972.8</v>
+        <v>57899.01</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9448.25</v>
+        <v>9436.219999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>16691.29</v>
+        <v>16750.86</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40466.74</v>
+        <v>40611.16</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9917.309999999999</v>
+        <v>9952.700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10687.22</v>
+        <v>10722.37</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14705.61</v>
+        <v>14753.97</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28.86</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21234.57</v>
+        <v>21381.67</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21374.43</v>
+        <v>21528.53</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>80538.85000000001</v>
+        <v>80206.89999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3745.6</v>
+        <v>3764.95</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9535.51</v>
+        <v>9584.75</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>63054.81</v>
+        <v>63499.82</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2662.02</v>
+        <v>2680.8</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>99.56</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10329.11</v>
+        <v>10402.01</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>149621.1</v>
+        <v>150677.07</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>22826.07</v>
+        <v>22531.03</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>160.65</v>
+        <v>158.61</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>951.5700000000001</v>
+        <v>939.48</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>642.62</v>
+        <v>634.46</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>553.22</v>
+        <v>546.1900000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3104.74</v>
+        <v>3065.3</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>296.59</v>
+        <v>292.83</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>729.13</v>
+        <v>719.86</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>444.89</v>
+        <v>440.46</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15927.3</v>
+        <v>15768.83</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>247.16</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1445.89</v>
+        <v>1431.51</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>39.73</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>160.65</v>
+        <v>159.06</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>123.58</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>31108</v>
+        <v>30798.49</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>58483.04</v>
+        <v>57901.16</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>13098.11</v>
+        <v>13051.14</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>234.8</v>
+        <v>233.96</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>247.16</v>
+        <v>246.63</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5322.23</v>
+        <v>5299.91</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>14844.75</v>
+        <v>14782.52</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>34928.28</v>
+        <v>34524.05</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10844.25</v>
+        <v>10718.75</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>926.85</v>
+        <v>919</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>197.73</v>
+        <v>196.05</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>74.15000000000001</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>36098.09</v>
+        <v>35792.31</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9394.620000000001</v>
+        <v>9315.040000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1174.02</v>
+        <v>1164.07</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>173.01</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>67891.14</v>
+        <v>67316.03999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>939.21</v>
+        <v>931.26</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8112.97</v>
+        <v>8044.24</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>160.65</v>
+        <v>159.29</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22879.94</v>
+        <v>22686.12</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>512.22</v>
+        <v>511.81</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>90.87</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3274.53</v>
+        <v>3287.1</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13441.93</v>
+        <v>13493.52</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2514.66</v>
+        <v>2521.33</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>995.46</v>
+        <v>998.1</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>752.8099999999999</v>
+        <v>754.8099999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26196.21</v>
+        <v>26159.46</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6723.69</v>
+        <v>6769.97</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>454.35</v>
+        <v>457.48</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2507.84</v>
+        <v>2538.66</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13796.65</v>
+        <v>13966.21</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>25440.19</v>
+        <v>25579.31</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>65159.2</v>
+        <v>63495.31</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>30091.67</v>
+        <v>29387.72</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>15778.78</v>
+        <v>15551.41</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>30054.05</v>
+        <v>29620.97</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>14706.45</v>
+        <v>14516.38</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7679.82</v>
+        <v>7580.57</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8776.02</v>
+        <v>8776.08</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>12081.92</v>
+        <v>12081.99</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10252.66</v>
+        <v>10266.9</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>20362.78</v>
+        <v>20292.89</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>767.34</v>
+        <v>772.37</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>43549.09</v>
+        <v>44212.08</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>40932.27</v>
+        <v>41555.42</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>32241.07</v>
+        <v>33218.72</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>16968.99</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>15200.97</v>
+        <v>15661.91</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1160.07</v>
+        <v>1155.94</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>15080.86</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>17972.44</v>
+        <v>18021.78</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2784.9</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2784.9</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>12107.26</v>
+        <v>12217.38</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1186.92</v>
+        <v>1197.72</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>27502.44</v>
+        <v>27683.57</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1267371.99</v>
+        <v>1275718.72</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15281.56</v>
+        <v>15382.2</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1160.07</v>
+        <v>1170.4</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>8761.4</v>
+        <v>8746.379999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>9515.209999999999</v>
+        <v>9498.9</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>17400.99</v>
+        <v>17371.16</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>46.29</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4640.26</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>70710.53999999999</v>
+        <v>70203.98</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>19721.12</v>
+        <v>19601.29</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5078.3</v>
+        <v>5058.7</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>31322.36</v>
+        <v>32232.16</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3869.07</v>
+        <v>3981.45</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>164854.51</v>
+        <v>162732.16</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3903.89</v>
+        <v>3853.63</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>12089.33</v>
+        <v>11933.69</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>16757.46</v>
+        <v>16639.2</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>12391.12</v>
+        <v>12303.68</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>7392.08</v>
+        <v>7391.7</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>12811.1</v>
+        <v>12810.44</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>338.28</v>
+        <v>336.77</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1133.12</v>
+        <v>1128.05</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9198.33</v>
+        <v>9236.33</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3425.68</v>
+        <v>3416.23</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>16485.45</v>
+        <v>16295.14</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1160.58</v>
+        <v>1153.91</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>17584.48</v>
+        <v>17483.47</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>12089.33</v>
+        <v>12011.88</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1645.25</v>
+        <v>1634.71</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>37421.86</v>
+        <v>37260.65</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6600.66</v>
+        <v>6572.23</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>42906.41</v>
+        <v>42721.57</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1648.55</v>
+        <v>1610.19</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4403.87</v>
+        <v>4301.39</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1121.01</v>
+        <v>1094.93</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>31741.22</v>
+        <v>30729.09</v>
       </c>
     </row>
     <row r="138">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>18866.98</v>
+        <v>18945.39</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2139-328-CM26</t>
+          <t>3481-41-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>8455.860000000001</v>
+        <v>3335.6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3481-41-CM26</t>
+          <t>3443-280-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3341.18</v>
+        <v>14692.85</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3443-280-CM26</t>
+          <t>1079639-273-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9017,17 +9017,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>14717.45</v>
+        <v>41482.95</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1079639-273-CM26</t>
+          <t>1079639-275-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>41552.43</v>
+        <v>26351.86</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1079639-275-CM26</t>
+          <t>1079639-276-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>26396</v>
+        <v>18252.37</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1079639-276-CM26</t>
+          <t>2139-328-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>18282.94</v>
+        <v>8441.719999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2140-295-CM26</t>
+          <t>1665-9977-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11477.62</v>
+        <v>10217.36</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1665-9977-CM26</t>
+          <t>2140-295-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10083.13</v>
+        <v>11630.42</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>15238.85</v>
+        <v>15441.72</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>28732.26</v>
+        <v>29107.2</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>42279.97</v>
+        <v>42760.79</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>31741.22</v>
+        <v>32027.15</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>133.65</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>400.94</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>23388.27</v>
+        <v>23287.79</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4702.34</v>
+        <v>4638.41</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>14482.46</v>
+        <v>14358.93</v>
       </c>
     </row>
     <row r="156">
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>17932.4</v>
+        <v>18068.22</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1665-10041-CM26</t>
+          <t>2140-396-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>9863.67</v>
+        <v>11511.55</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2140-396-CM26</t>
+          <t>1665-10041-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>11468.1</v>
+        <v>9901.030000000001</v>
       </c>
     </row>
     <row r="159">
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>18897.6</v>
+        <v>18849.88</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1079639-413-CM26</t>
+          <t>1079639-414-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>44067.94</v>
+        <v>23828.38</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1079639-414-CM26</t>
+          <t>1079639-413-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>23888.7</v>
+        <v>43956.67</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9588.5</v>
+        <v>9679.6</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>15139.31</v>
+        <v>15283.14</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1671.05</v>
+        <v>1683.5</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>50663.97</v>
+        <v>50158.71</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5254.9</v>
+        <v>5202.5</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5340.63</v>
+        <v>5287.37</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>12538.07</v>
+        <v>12509.62</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>19524.58</v>
+        <v>19476.37</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6099.76</v>
+        <v>6084.7</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>20052.63</v>
+        <v>20003.11</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>133.68</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>31750</v>
+        <v>31855.32</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>649.22</v>
+        <v>652.67</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>22280.7</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>628.85</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>13283.38</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1660.42</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>16941.29</v>
+        <v>16655.06</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7767.13</v>
+        <v>7660.4</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>13774.14</v>
+        <v>13584.88</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>208.22</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="183">
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>12145.99</v>
+        <v>12070.69</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1665-10117-CM26</t>
+          <t>1663-729-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>9426.549999999999</v>
+        <v>420264.55</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1663-729-CM26</t>
+          <t>1665-10117-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>410995.54</v>
+        <v>9639.15</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>19925.08</v>
+        <v>19986.68</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>42728.48</v>
+        <v>42615.47</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>27063.83</v>
+        <v>26992.25</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>18745.51</v>
+        <v>18695.93</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>308.63</v>
+        <v>302.59</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>18818.13</v>
+        <v>18539.32</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>31579.96</v>
+        <v>31879.94</v>
       </c>
     </row>
     <row r="193">
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>107.28</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1661-416-CM26</t>
+          <t>1057531-302-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12285,13 +12285,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>18411.12</v>
+        <v>12824.49</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2140-592-CM26</t>
+          <t>2140-591-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>12006.7</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1057531-302-CM26</t>
+          <t>2140-592-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>12889.78</v>
+        <v>11945.88</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2140-591-CM26</t>
+          <t>1661-416-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>221.06</v>
+        <v>18317.85</v>
       </c>
     </row>
     <row r="198">
@@ -12529,13 +12529,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>14227.61</v>
+        <v>14320.37</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2139-583-CM26</t>
+          <t>1079639-609-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12560,12 +12560,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12590,13 +12590,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>9271.879999999999</v>
+        <v>18922.21</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1079639-606-CM26</t>
+          <t>1079639-607-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12651,13 +12651,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>41960.52</v>
+        <v>27696.62</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1079639-607-CM26</t>
+          <t>2139-583-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12682,12 +12682,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>27512.47</v>
+        <v>9333.940000000001</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1079639-609-CM26</t>
+          <t>1079639-606-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>18796.4</v>
+        <v>42241.38</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>10326.65</v>
+        <v>10294.03</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2050.09</v>
+        <v>2045.63</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5112.95</v>
+        <v>5083.35</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>195.8</v>
+        <v>192.64</v>
       </c>
     </row>
     <row r="207">
@@ -13078,13 +13078,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>21482.97</v>
+        <v>21138.52</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>507428-772-CM26</t>
+          <t>2324-991-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13104,17 +13104,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>31579.96</v>
+        <v>1512.85</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2324-991-CM26</t>
+          <t>507428-772-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13165,17 +13165,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13185,12 +13185,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1530.66</v>
+        <v>31212.51</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>26953.27</v>
+        <v>26803.85</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8893.950000000001</v>
+        <v>8850.219999999999</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,68 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>28317.4</v>
+        <v>28506.94</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1079639-696-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>18953.98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M213"/>
+  <dimension ref="A1:M224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057531-939-CM25</t>
+          <t>1057534-346-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12227.16</v>
+        <v>19544.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>507428-3913-CM25</t>
+          <t>1057532-4289-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>30302.06</v>
+        <v>44203.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3481-180-CM25</t>
+          <t>2940-84-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>69.210.201-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1058.06</v>
+        <v>1963.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3481-185-CM25</t>
+          <t>1514-14355-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14635.02</v>
+        <v>41534.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2297-1581-CM25</t>
+          <t>707425-92-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1199.93</v>
+        <v>12553.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2140-1523-CM25</t>
+          <t>1057531-748-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10734.49</v>
+        <v>12870.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079639-959-CM25</t>
+          <t>3481-106-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20583.25</v>
+        <v>1035.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1514-16987-CM25</t>
+          <t>1057531-784-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>57899.01</v>
+        <v>12403.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2139-5010-CM25</t>
+          <t>507428-3527-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9436.219999999999</v>
+        <v>24675.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1661-631-CM25</t>
+          <t>1514-16050-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>16750.86</v>
+        <v>52917.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1514-17015-CM25</t>
+          <t>3481-161-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40611.16</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1665-912-CM25</t>
+          <t>1057531-939-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9952.700000000001</v>
+        <v>12227.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2138-303-CM25</t>
+          <t>507428-3913-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10722.37</v>
+        <v>30302.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2137-9107-CM25</t>
+          <t>2297-1581-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14753.97</v>
+        <v>1199.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>707425-236-CM25</t>
+          <t>3481-185-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>29.35</v>
+        <v>14635.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1388974-359-CM25</t>
+          <t>3481-180-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>71.146.000-4</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21381.67</v>
+        <v>1058.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057534-1496-CM25</t>
+          <t>2140-1523-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21528.53</v>
+        <v>10734.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>545598-848-CM25</t>
+          <t>1079639-959-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>80206.89999999999</v>
+        <v>20583.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>620279-243-CM25</t>
+          <t>1514-16987-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3764.95</v>
+        <v>57899.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>584385-229-CM25</t>
+          <t>2139-5010-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.979.730-2</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA Va ZONA NAVAL</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9584.75</v>
+        <v>9436.219999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1079639-1002-CM25</t>
+          <t>1661-631-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>63499.82</v>
+        <v>16750.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1079639-1056-CM25</t>
+          <t>1665-912-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2680.8</v>
+        <v>9952.700000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079639-1058-CM25</t>
+          <t>1514-17015-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>100.26</v>
+        <v>40611.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2660-69-CM25</t>
+          <t>2137-9107-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10402.01</v>
+        <v>14753.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1663-1769-CM25</t>
+          <t>2138-303-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>Hospital de Queilen</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>150677.07</v>
+        <v>10722.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2297-1702-CM25</t>
+          <t>707425-236-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>22531.03</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1079639-1090-CM25</t>
+          <t>1388974-359-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>71.146.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>158.61</v>
+        <v>21381.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079639-1074-CM25</t>
+          <t>1057534-1496-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>939.48</v>
+        <v>21528.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079639-1073-CM25</t>
+          <t>545598-848-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>634.46</v>
+        <v>80206.89999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1079639-1067-CM25</t>
+          <t>584385-229-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.979.730-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>COMANDANCIA EN JEFE DE LA Va ZONA NAVAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>546.1900000000001</v>
+        <v>9584.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1079639-1071-CM25</t>
+          <t>620279-243-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>BASE NAVAL PUERTO MONTT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3065.3</v>
+        <v>3764.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1079639-1065-CM25</t>
+          <t>2660-69-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>292.83</v>
+        <v>10402.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079639-1072-CM25</t>
+          <t>1079639-1056-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>719.86</v>
+        <v>2680.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1079639-1075-CM25</t>
+          <t>1079639-1002-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>440.46</v>
+        <v>63499.82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3481-190-CM25</t>
+          <t>1079639-1058-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15768.83</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1079639-1085-CM25</t>
+          <t>1663-1769-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>244.7</v>
+        <v>150677.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079639-1086-CM25</t>
+          <t>2297-1702-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1431.51</v>
+        <v>22531.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079639-1087-CM25</t>
+          <t>1079639-1072-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>39.34</v>
+        <v>719.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079639-1088-CM25</t>
+          <t>1079639-1067-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>159.06</v>
+        <v>546.1900000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1079639-1089-CM25</t>
+          <t>1079639-1073-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>122.35</v>
+        <v>634.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>507428-4070-CM25</t>
+          <t>1079639-1074-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>30798.49</v>
+        <v>939.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1514-17234-CM25</t>
+          <t>1079639-1090-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>57901.16</v>
+        <v>158.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057531-984-CM25</t>
+          <t>1079639-1065-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>13051.14</v>
+        <v>292.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1079639-1096-CM25</t>
+          <t>1079639-1071-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>233.96</v>
+        <v>3065.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079639-1094-CM25</t>
+          <t>1079639-1075-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>246.63</v>
+        <v>440.46</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>545598-909-CM25</t>
+          <t>3481-190-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5299.91</v>
+        <v>15768.83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1661-713-CM25</t>
+          <t>1079639-1085-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>14782.52</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3480-346-CM25</t>
+          <t>1079639-1086-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.101.471-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>34524.05</v>
+        <v>1431.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2140-1635-CM25</t>
+          <t>1079639-1087-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10718.75</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079639-1131-CM25</t>
+          <t>1514-17234-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>919</v>
+        <v>57901.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079639-1129-CM25</t>
+          <t>507428-4070-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>196.05</v>
+        <v>30798.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1079639-1128-CM25</t>
+          <t>1079639-1089-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>73.52</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1514-17299-CM25</t>
+          <t>1079639-1088-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>35792.31</v>
+        <v>159.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1665-982-CM25</t>
+          <t>1057531-984-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9315.040000000001</v>
+        <v>13051.14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1079639-1124-CM25</t>
+          <t>1079639-1096-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1164.07</v>
+        <v>233.96</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079639-1113-CM25</t>
+          <t>1079639-1094-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>171.55</v>
+        <v>246.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079639-1123-CM25</t>
+          <t>545598-909-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>67316.03999999999</v>
+        <v>5299.91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079639-1120-CM25</t>
+          <t>1661-713-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>931.26</v>
+        <v>14782.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079639-1114-CM25</t>
+          <t>2140-1635-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>85.77</v>
+        <v>10718.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2139-5112-CM25</t>
+          <t>3480-346-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.101.471-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8044.24</v>
+        <v>34524.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1079639-1111-CM25</t>
+          <t>1079639-1131-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>159.29</v>
+        <v>919</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1079639-1107-CM25</t>
+          <t>1079639-1123-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22686.12</v>
+        <v>67316.03999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3443-1095-CM25</t>
+          <t>1079639-1128-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>511.81</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3443-1098-CM25</t>
+          <t>1079639-1129-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>90.8</v>
+        <v>196.05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3481-193-CM25</t>
+          <t>1079639-1111-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3287.1</v>
+        <v>159.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2137-9191-CM25</t>
+          <t>1079639-1113-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13493.52</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>893-103-CM25</t>
+          <t>1079639-1114-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2521.33</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2028-258-CM25</t>
+          <t>1079639-1120-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.902.039-3</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Llanquihue</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>998.1</v>
+        <v>931.26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1661-753-CM25</t>
+          <t>2139-5112-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>754.8099999999999</v>
+        <v>8044.24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057534-1599-CM25</t>
+          <t>1079639-1124-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26159.46</v>
+        <v>1164.07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3508-1454-CM25</t>
+          <t>1665-982-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.230.500-0</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHONCHI</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6769.97</v>
+        <v>9315.040000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5110-600-CM25</t>
+          <t>1514-17299-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>457.48</v>
+        <v>35792.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>707425-281-CM25</t>
+          <t>1079639-1107-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2538.66</v>
+        <v>22686.12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2943-34-CM25</t>
+          <t>3443-1095-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.210.200-2</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PABLO</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13966.21</v>
+        <v>511.81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2138-359-CM25</t>
+          <t>3443-1098-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>11055.34</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3508-1483-CM25</t>
+          <t>3481-193-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.230.500-0</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHONCHI</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>25579.31</v>
+        <v>3287.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1514-1-CM26</t>
+          <t>2137-9191-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>63495.31</v>
+        <v>13493.52</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>507428-24-CM26</t>
+          <t>2028-258-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>60.902.039-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Depto. Provincial Educación Llanquihue</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>29387.72</v>
+        <v>998.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1661-5-CM26</t>
+          <t>893-103-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,27 +5282,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>15551.41</v>
+        <v>2521.33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1514-115-CM26</t>
+          <t>1661-753-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>29620.97</v>
+        <v>754.8099999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1057531-6-CM26</t>
+          <t>1057534-1599-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>14516.38</v>
+        <v>26159.46</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2139-22-CM26</t>
+          <t>5110-600-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7580.57</v>
+        <v>457.48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1665-9786-CM26</t>
+          <t>3508-1454-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,27 +5526,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>69.230.500-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE CHONCHI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8776.08</v>
+        <v>6769.97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2137-16-CM26</t>
+          <t>2943-34-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>69.210.200-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>12081.99</v>
+        <v>13966.21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2140-16-CM26</t>
+          <t>707425-281-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10266.9</v>
+        <v>2538.66</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2138-59-CM26</t>
+          <t>2138-359-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>20292.89</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1503362-1-CM26</t>
+          <t>3508-1483-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.230.500-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>I MUNICIPALIDAD DE CHONCHI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>772.37</v>
+        <v>25579.31</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1079639-14-CM26</t>
+          <t>1514-1-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>44212.08</v>
+        <v>63495.31</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1079639-16-CM26</t>
+          <t>507428-24-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>41555.42</v>
+        <v>29387.72</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>507428-117-CM26</t>
+          <t>1661-5-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>33218.72</v>
+        <v>15551.41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057534-105-CM26</t>
+          <t>1514-115-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>17483.54</v>
+        <v>29620.97</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>620279-22-CM26</t>
+          <t>2139-22-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>15661.91</v>
+        <v>7580.57</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3481-10-CM26</t>
+          <t>1057531-6-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1155.94</v>
+        <v>14516.38</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057531-59-CM26</t>
+          <t>1665-9786-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>15017.27</v>
+        <v>8776.08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1661-81-CM26</t>
+          <t>2137-16-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>18021.78</v>
+        <v>12081.99</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1057536-375-CM26</t>
+          <t>2140-16-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2810.23</v>
+        <v>10266.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057536-376-CM26</t>
+          <t>2138-59-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>Hospital de Queilen</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2810.23</v>
+        <v>20292.89</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2140-111-CM26</t>
+          <t>1503362-1-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DEL PATRIMONIO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>12217.38</v>
+        <v>772.37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057532-207-CM26</t>
+          <t>1079639-14-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1197.72</v>
+        <v>44212.08</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>620279-15-CM26</t>
+          <t>1079639-16-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>27683.57</v>
+        <v>41555.42</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1514-638-SE26</t>
+          <t>507428-117-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6662,24 +6662,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1275718.72</v>
+        <v>33218.72</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2137-117-CM26</t>
+          <t>1057534-105-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6689,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6704,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15382.2</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3481-14-CM26</t>
+          <t>620279-22-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6750,27 +6746,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>BASE NAVAL PUERTO MONTT</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6795,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1170.4</v>
+        <v>15661.91</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1665-9865-CM26</t>
+          <t>3481-10-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6816,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6826,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>8746.379999999999</v>
+        <v>1155.94</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2139-171-CM26</t>
+          <t>1057531-59-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6887,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6917,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>9498.9</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2138-106-CM26</t>
+          <t>1661-81-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6938,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6978,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>17371.16</v>
+        <v>18021.78</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1661-99-CM26</t>
+          <t>1057536-375-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7009,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7039,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>46.24</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3481-22-CM26</t>
+          <t>1057536-376-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7060,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7070,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7100,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4607.02</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079639-81-CM26</t>
+          <t>2140-111-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7121,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7161,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>70203.98</v>
+        <v>12217.38</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1057534-243-CM26</t>
+          <t>1057532-207-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7182,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7192,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7222,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>19601.29</v>
+        <v>1197.72</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1079639-95-CM26</t>
+          <t>2137-117-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7253,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7283,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5058.7</v>
+        <v>15382.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>507428-214-CM26</t>
+          <t>1514-638-SE26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7299,12 +7295,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7314,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7337,20 +7333,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>32232.16</v>
+        <v>1275718.72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1057536-603-CM26</t>
+          <t>620279-15-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>BASE NAVAL PUERTO MONTT</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3981.45</v>
+        <v>27683.57</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1663-172-CM26</t>
+          <t>3481-14-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>162732.16</v>
+        <v>1170.4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>752-52-CM26</t>
+          <t>2138-106-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>Hospital de Queilen</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3853.63</v>
+        <v>17371.16</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057531-99-CM26</t>
+          <t>1665-9865-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11933.69</v>
+        <v>8746.379999999999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1661-159-CM26</t>
+          <t>2139-171-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>16639.2</v>
+        <v>9498.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2140-190-CM26</t>
+          <t>1661-99-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>12303.68</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2139-238-CM26</t>
+          <t>3481-22-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>7391.7</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2137-188-CM26</t>
+          <t>1079639-81-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>12810.44</v>
+        <v>70203.98</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1661-163-CM26</t>
+          <t>1057534-243-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>336.77</v>
+        <v>19601.29</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4443-16-CM26</t>
+          <t>1079639-95-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1128.05</v>
+        <v>5058.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1665-9938-CM26</t>
+          <t>507428-214-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9236.33</v>
+        <v>32232.16</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057532-420-CM26</t>
+          <t>1057536-603-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3416.23</v>
+        <v>3981.45</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2138-150-CM26</t>
+          <t>1057531-99-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>16295.14</v>
+        <v>11933.69</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2028-9-CM26</t>
+          <t>752-52-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.902.039-3</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Llanquihue</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1153.91</v>
+        <v>3853.63</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057534-351-CM26</t>
+          <t>1663-172-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>17483.47</v>
+        <v>162732.16</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1057531-128-CM26</t>
+          <t>2140-190-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>12011.88</v>
+        <v>12303.68</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3480-36-CM26</t>
+          <t>1661-159-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.101.471-6</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1634.71</v>
+        <v>16639.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1079639-160-CM26</t>
+          <t>2139-238-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>37260.65</v>
+        <v>7391.7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1079639-193-CM26</t>
+          <t>2137-188-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6572.23</v>
+        <v>12810.44</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1079639-159-CM26</t>
+          <t>1661-163-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>42721.57</v>
+        <v>336.77</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3481-37-CM26</t>
+          <t>4443-16-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1610.19</v>
+        <v>1128.05</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1503362-42-CM26</t>
+          <t>1665-9938-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4301.39</v>
+        <v>9236.33</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1503362-43-CM26</t>
+          <t>1057532-420-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1094.93</v>
+        <v>3416.23</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>507428-314-CM26</t>
+          <t>2138-150-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Hospital de Queilen</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>30729.09</v>
+        <v>16295.14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1661-215-CM26</t>
+          <t>2028-9-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>60.902.039-3</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Depto. Provincial Educación Llanquihue</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>18945.39</v>
+        <v>1153.91</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3481-41-CM26</t>
+          <t>1057534-351-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3335.6</v>
+        <v>17483.47</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3443-280-CM26</t>
+          <t>1057531-128-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8946,27 +8946,27 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>14692.85</v>
+        <v>12011.88</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1079639-273-CM26</t>
+          <t>3480-36-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.471-6</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>41482.95</v>
+        <v>1634.71</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1079639-275-CM26</t>
+          <t>1079639-159-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>26351.86</v>
+        <v>42721.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1079639-276-CM26</t>
+          <t>1079639-160-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>18252.37</v>
+        <v>37260.65</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2139-328-CM26</t>
+          <t>1079639-193-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>8441.719999999999</v>
+        <v>6572.23</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1665-9977-CM26</t>
+          <t>3481-37-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>10217.36</v>
+        <v>1610.19</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2140-295-CM26</t>
+          <t>1503362-42-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DEL PATRIMONIO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11630.42</v>
+        <v>4301.39</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2137-275-CM26</t>
+          <t>1503362-43-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DEL PATRIMONIO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>15441.72</v>
+        <v>1094.93</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3479-646-CM26</t>
+          <t>507428-314-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>29107.2</v>
+        <v>30729.09</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>545598-237-CM26</t>
+          <t>1661-215-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>42760.79</v>
+        <v>18945.39</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>507428-400-CM26</t>
+          <t>2139-328-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>32027.15</v>
+        <v>8441.719999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1479-46-CM26</t>
+          <t>1079639-275-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.902.011-3</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>134.07</v>
+        <v>26351.86</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1479-47-CM26</t>
+          <t>1079639-276-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.902.011-3</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>402.2</v>
+        <v>18252.37</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1057534-502-CM26</t>
+          <t>3443-280-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9744,22 +9744,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>23287.79</v>
+        <v>14692.85</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>584146-183-CM26</t>
+          <t>3481-41-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9800,27 +9800,27 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4638.41</v>
+        <v>3335.6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057531-167-CM26</t>
+          <t>1079639-273-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>14358.93</v>
+        <v>41482.95</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1661-283-CM26</t>
+          <t>2137-275-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>18068.22</v>
+        <v>15441.72</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2140-396-CM26</t>
+          <t>1665-9977-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9983,12 +9983,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>11511.55</v>
+        <v>10217.36</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1665-10041-CM26</t>
+          <t>2140-295-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10044,12 +10044,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>9901.030000000001</v>
+        <v>11630.42</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1079639-415-CM26</t>
+          <t>3479-646-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>18849.88</v>
+        <v>29107.2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1079639-414-CM26</t>
+          <t>545598-237-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10166,12 +10166,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>23828.38</v>
+        <v>42760.79</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1079639-413-CM26</t>
+          <t>507428-400-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>43956.67</v>
+        <v>32027.15</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2139-427-CM26</t>
+          <t>1479-46-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>60.902.011-3</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Departamento Provincial de Educación Osorno</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9679.6</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2137-377-CM26</t>
+          <t>1479-47-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>60.902.011-3</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>Departamento Provincial de Educación Osorno</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>15283.14</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3481-61-CM26</t>
+          <t>1057534-502-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1683.5</v>
+        <v>23287.79</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>853-99-CM26</t>
+          <t>584146-183-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10476,22 +10476,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>50158.71</v>
+        <v>4638.41</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>853-100-CM26</t>
+          <t>1057531-167-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5202.5</v>
+        <v>14358.93</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>707425-93-CM26</t>
+          <t>1661-283-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5287.37</v>
+        <v>18068.22</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>584146-208-CM26</t>
+          <t>1665-10041-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10659,22 +10659,22 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10699,13 +10699,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>12509.62</v>
+        <v>9901.030000000001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>853-102-CM26</t>
+          <t>2140-396-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>19476.37</v>
+        <v>11511.55</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>853-103-CM26</t>
+          <t>1079639-413-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6084.7</v>
+        <v>43956.67</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2138-228-CM26</t>
+          <t>1079639-414-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10882,13 +10882,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>20003.11</v>
+        <v>23828.38</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1479-72-CM26</t>
+          <t>1079639-415-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.902.011-3</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>134.34</v>
+        <v>18849.88</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>507428-551-CM26</t>
+          <t>2139-427-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>31855.32</v>
+        <v>9679.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5110-197-CM26</t>
+          <t>2137-377-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>652.67</v>
+        <v>15283.14</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057534-666-CM26</t>
+          <t>3481-61-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>22399.18</v>
+        <v>1683.5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>584146-226-CM26</t>
+          <t>853-99-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11147,22 +11147,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>632.1900000000001</v>
+        <v>50158.71</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1057531-230-CM26</t>
+          <t>853-100-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11218,12 +11218,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>13508.04</v>
+        <v>5202.5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3481-72-CM26</t>
+          <t>707425-93-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1676</v>
+        <v>5287.37</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1661-346-CM26</t>
+          <t>584146-208-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11325,27 +11325,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>16655.06</v>
+        <v>12509.62</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2139-514-CM26</t>
+          <t>853-103-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7660.4</v>
+        <v>6084.7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2137-461-CM26</t>
+          <t>2138-228-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>Hospital de Queilen</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>13584.88</v>
+        <v>20003.11</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2140-514-CM26</t>
+          <t>853-102-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>205.36</v>
+        <v>19476.37</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2140-515-CM26</t>
+          <t>1479-72-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11569,12 +11569,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>60.902.011-3</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Departamento Provincial de Educación Osorno</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>12070.69</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1663-729-CM26</t>
+          <t>507428-551-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>420264.55</v>
+        <v>31855.32</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1665-10117-CM26</t>
+          <t>5110-197-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11691,27 +11691,27 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11736,28 +11736,28 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>9639.15</v>
+        <v>652.67</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2138-267-CM26</t>
+          <t>1057534-666-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11767,12 +11767,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11797,43 +11797,43 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>19986.68</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1079639-555-CM26</t>
+          <t>584146-226-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11858,18 +11858,18 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>42615.47</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1079639-556-CM26</t>
+          <t>1057531-230-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11919,18 +11919,18 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>26992.25</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1079639-557-CM26</t>
+          <t>3481-72-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11980,18 +11980,18 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>18695.93</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>584146-277-CM26</t>
+          <t>1661-346-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12001,22 +12001,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12041,18 +12041,18 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>302.59</v>
+        <v>16655.06</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057534-825-CM26</t>
+          <t>2139-514-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12102,28 +12102,28 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>18539.32</v>
+        <v>7660.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>507428-683-CM26</t>
+          <t>2137-461-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12163,43 +12163,43 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>31879.94</v>
+        <v>13584.88</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>707425-120-CM26</t>
+          <t>2140-514-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12224,28 +12224,28 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>108.3</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1057531-302-CM26</t>
+          <t>2140-515-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12285,28 +12285,28 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>12824.49</v>
+        <v>12070.69</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2140-591-CM26</t>
+          <t>1665-10117-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12346,28 +12346,28 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>219.94</v>
+        <v>9639.15</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2140-592-CM26</t>
+          <t>1663-729-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>11945.88</v>
+        <v>420264.55</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1661-416-CM26</t>
+          <t>2138-267-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>Hospital de Queilen</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>18317.85</v>
+        <v>19986.68</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2137-583-CM26</t>
+          <t>1079639-555-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12484,12 +12484,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12499,12 +12499,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12529,13 +12529,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>14320.37</v>
+        <v>42615.47</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1079639-609-CM26</t>
+          <t>1079639-556-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12590,13 +12590,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>18922.21</v>
+        <v>26992.25</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1079639-607-CM26</t>
+          <t>1079639-557-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12651,13 +12651,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>27696.62</v>
+        <v>18695.93</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2139-583-CM26</t>
+          <t>584146-277-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12667,27 +12667,27 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>9333.940000000001</v>
+        <v>302.59</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1079639-606-CM26</t>
+          <t>1057534-825-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12773,13 +12773,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>42241.38</v>
+        <v>18539.32</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1665-10149-CM26</t>
+          <t>507428-683-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12794,22 +12794,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12834,13 +12834,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>10294.03</v>
+        <v>31879.94</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1057532-1156-CM26</t>
+          <t>707425-120-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12895,13 +12895,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2045.63</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1413-685-CM26</t>
+          <t>1057531-302-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12916,22 +12916,22 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.004.098-5</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5083.35</v>
+        <v>12824.49</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1661-455-CM26</t>
+          <t>2140-591-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -13017,13 +13017,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>192.64</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1057534-948-CM26</t>
+          <t>2140-592-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13078,13 +13078,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>21138.52</v>
+        <v>11945.88</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2324-991-CM26</t>
+          <t>1661-416-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13099,22 +13099,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1512.85</v>
+        <v>18317.85</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>507428-772-CM26</t>
+          <t>2137-583-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13170,12 +13170,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>Hospital de Achao</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13200,13 +13200,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>31212.51</v>
+        <v>14320.37</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2927-362-CM26</t>
+          <t>2139-583-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13221,22 +13221,22 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.230.700-3</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Servicio de Salud del Reloncaví</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13261,13 +13261,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>26803.85</v>
+        <v>9333.940000000001</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2730-379-CM26</t>
+          <t>1079639-606-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13282,22 +13282,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13322,13 +13322,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8850.219999999999</v>
+        <v>42241.38</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>620279-151-CM26</t>
+          <t>1079639-607-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13383,13 +13383,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>28506.94</v>
+        <v>27696.62</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1079639-696-CM26</t>
+          <t>1079639-609-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13444,6 +13444,677 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
+        <v>18922.21</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1665-10149-CM26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>61.602.311-k</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Servicio de Salud del Reloncaví</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>10294.03</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1057532-1156-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>2045.63</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1413-685-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>61.004.098-5</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>5083.35</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1661-455-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>61.602.268-7</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Servicio de Salud del Reloncaví</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>192.64</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1057534-948-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>61.607.602-7</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>21138.52</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2324-991-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>1512.85</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>507428-772-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>31212.51</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2927-362-CM26</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>69.230.700-3</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUELLON</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>26803.85</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2730-379-CM26</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>69.230.400-4</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>8850.219999999999</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>620279-151-CM26</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>61.980.010-9</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>BASE NAVAL PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>28506.94</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1079639-696-CM26</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="n">
         <v>18953.98</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +24027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +24092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +24157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +24222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +24287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +25002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +25067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +25132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +25197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +25262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +25327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +25392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +26042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +26107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +26172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +26237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +26302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25271,7 +26887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +27017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +27082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +27147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +27212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +27277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +27342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +27472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +28057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +28122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +28187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +28252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +28317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +29032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +29097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +29162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +29227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +29292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +29357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +30007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +30072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +30137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +30202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +30267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +30332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +30462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30783,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30848,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30913,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30978,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +31043,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +31108,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +31173,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +31238,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +31303,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +31368,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31433,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31498,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31563,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31628,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31693,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31758,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31823,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31888,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31953,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +32018,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +32083,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +32148,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +32213,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +32278,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +32343,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32408,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32473,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32538,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32603,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32668,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32733,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32798,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32863,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32928,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32993,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +33058,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +33184,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +33249,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +33314,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33379,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33444,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33509,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33574,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33639,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33704,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33769,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33895,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33960,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +34025,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +34090,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +34155,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +34220,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +34346,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
@@ -30722,7 +30722,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33123,7 +33127,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33834,7 +33842,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34285,7 +34297,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M522"/>
+  <dimension ref="A1:M543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>752-40-CM25</t>
+          <t>507428-2452-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1350.59</v>
+        <v>26569.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057534-111-CM25</t>
+          <t>752-40-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10091.43</v>
+        <v>1350.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>507428-2452-CM25</t>
+          <t>1057534-111-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26569.88</v>
+        <v>10091.43</v>
       </c>
     </row>
     <row r="24">
@@ -2334,7 +2334,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3481-17-CM25</t>
+          <t>3481-18-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1039.54</v>
+        <v>3118.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3481-18-CM25</t>
+          <t>1514-6777-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3118.86</v>
+        <v>41244.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1514-6777-CM25</t>
+          <t>1665-110-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41244.29</v>
+        <v>9410.219999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1665-110-CM25</t>
+          <t>2137-125-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2549,17 +2549,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9410.219999999999</v>
+        <v>12900.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2137-125-CM25</t>
+          <t>3481-17-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12900.95</v>
+        <v>1039.54</v>
       </c>
     </row>
     <row r="35">
@@ -2854,7 +2854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>853-55-CM25</t>
+          <t>853-56-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>36279.51</v>
+        <v>16744.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>853-56-CM25</t>
+          <t>853-55-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16744.39</v>
+        <v>36279.51</v>
       </c>
     </row>
     <row r="40">
@@ -3309,7 +3309,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057536-1488-CM25</t>
+          <t>1057536-1485-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2926.02</v>
+        <v>2001.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057536-1485-CM25</t>
+          <t>1057536-1488-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2001.21</v>
+        <v>2926.02</v>
       </c>
     </row>
     <row r="47">
@@ -4544,7 +4544,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1079639-228-CM25</t>
+          <t>1057534-346-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4109.54</v>
+        <v>19544.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057534-346-CM25</t>
+          <t>1079639-228-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>19544.4</v>
+        <v>4109.54</v>
       </c>
     </row>
     <row r="66">
@@ -5129,7 +5129,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1665-299-CM25</t>
+          <t>507428-2724-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10263.06</v>
+        <v>21077.15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>507428-2724-CM25</t>
+          <t>1665-299-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>21077.15</v>
+        <v>10263.06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1479-35-CM25</t>
+          <t>1514-13849-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.902.011-3</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>699.16</v>
+        <v>43338.57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1479-34-CM25</t>
+          <t>1479-35-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>480.22</v>
+        <v>699.16</v>
       </c>
     </row>
     <row r="77">
@@ -5454,7 +5454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1514-13849-CM25</t>
+          <t>1479-33-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>60.902.011-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>43338.57</v>
+        <v>1718.46</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1479-33-CM25</t>
+          <t>1479-34-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1718.46</v>
+        <v>480.22</v>
       </c>
     </row>
     <row r="80">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>707425-40-CM25</t>
+          <t>934-66-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>11252.64</v>
+        <v>422.74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>934-66-CM25</t>
+          <t>707425-40-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>422.74</v>
+        <v>11252.64</v>
       </c>
     </row>
     <row r="91">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1515-80-CM25</t>
+          <t>934-69-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.511.102-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE OSORNO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>561.59</v>
+        <v>1357.19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>934-69-CM25</t>
+          <t>1515-80-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.511.102-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE OSORNO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1357.19</v>
+        <v>561.59</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2137-431-CM25</t>
+          <t>5413-438-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8509.01</v>
+        <v>1512.92</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5413-438-CM25</t>
+          <t>2137-431-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1512.92</v>
+        <v>8509.01</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3443-393-CM25</t>
+          <t>934-73-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13620.75</v>
+        <v>1545.62</v>
       </c>
     </row>
     <row r="105">
@@ -7274,7 +7274,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>934-73-CM25</t>
+          <t>3443-393-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7294,17 +7294,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1545.62</v>
+        <v>13620.75</v>
       </c>
     </row>
     <row r="107">
@@ -7469,7 +7469,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1665-420-CM25</t>
+          <t>2660-35-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7874.82</v>
+        <v>36210.8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2660-35-CM25</t>
+          <t>1665-420-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>36210.8</v>
+        <v>7874.82</v>
       </c>
     </row>
     <row r="111">
@@ -7989,7 +7989,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3481-75-CM25</t>
+          <t>1479-92-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>60.902.011-3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,13 +8048,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1594.56</v>
+        <v>878.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1479-92-CM25</t>
+          <t>3481-75-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.902.011-3</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>878.7</v>
+        <v>1594.56</v>
       </c>
     </row>
     <row r="119">
@@ -8444,7 +8444,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>707425-72-CM25</t>
+          <t>584385-101-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.730-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11211.11</v>
+        <v>7929.79</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057534-606-CM25</t>
+          <t>707425-72-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>19144.66</v>
+        <v>11211.11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>584385-101-CM25</t>
+          <t>1057534-606-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.979.730-2</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7929.79</v>
+        <v>19144.66</v>
       </c>
     </row>
     <row r="127">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2136-486-CM25</t>
+          <t>2136-487-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>533.6799999999999</v>
+        <v>1145.81</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2136-487-CM25</t>
+          <t>2136-486-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1145.81</v>
+        <v>533.6799999999999</v>
       </c>
     </row>
     <row r="136">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>582-69-CM25</t>
+          <t>2927-212-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9569,17 +9569,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.511.104-1</t>
+          <t>69.230.700-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>469.54</v>
+        <v>21965.02</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2927-212-CM25</t>
+          <t>1665-484-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.230.700-3</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Quellón</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>21965.02</v>
+        <v>9093.58</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1665-484-CM25</t>
+          <t>1661-285-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>9093.58</v>
+        <v>15578.01</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1661-285-CM25</t>
+          <t>582-69-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>60.511.104-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>15578.01</v>
+        <v>469.54</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1514-14813-CM25</t>
+          <t>1479-113-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>60.902.011-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>40987.27</v>
+        <v>213.02</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1479-113-CM25</t>
+          <t>1514-14813-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.902.011-3</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>213.02</v>
+        <v>40987.27</v>
       </c>
     </row>
     <row r="147">
@@ -10719,7 +10719,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>707425-92-CM25</t>
+          <t>2138-146-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>12553.54</v>
+        <v>9670.450000000001</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2138-146-CM25</t>
+          <t>707425-92-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>9670.450000000001</v>
+        <v>12553.54</v>
       </c>
     </row>
     <row r="161">
@@ -11174,7 +11174,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1661-343-CM25</t>
+          <t>1665-559-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>15435.13</v>
+        <v>8667.24</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2140-1156-CM25</t>
+          <t>2140-1155-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>318.56</v>
+        <v>11468.16</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1665-559-CM25</t>
+          <t>2140-1156-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>8667.24</v>
+        <v>318.56</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2140-1155-CM25</t>
+          <t>1661-343-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>11468.16</v>
+        <v>15435.13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2139-4549-CM25</t>
+          <t>3443-551-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11454,17 +11454,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>7604.56</v>
+        <v>3065.81</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3443-551-CM25</t>
+          <t>2139-4549-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11519,17 +11519,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3065.81</v>
+        <v>7604.56</v>
       </c>
     </row>
     <row r="172">
@@ -12474,7 +12474,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2140-1228-CM25</t>
+          <t>2140-1227-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>9688.85</v>
+        <v>351.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2140-1227-CM25</t>
+          <t>2140-1228-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>351.9</v>
+        <v>9688.85</v>
       </c>
     </row>
     <row r="188">
@@ -12734,7 +12734,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1661-407-CM25</t>
+          <t>1224953-541-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12754,17 +12754,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>340.91</v>
+        <v>47340.71</v>
       </c>
     </row>
     <row r="191">
@@ -12864,7 +12864,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1224953-541-CM25</t>
+          <t>1661-407-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12884,17 +12884,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>47340.71</v>
+        <v>340.91</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1665-658-CM25</t>
+          <t>2139-4653-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12949,12 +12949,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>9080.620000000001</v>
+        <v>8588.98</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2139-4653-CM25</t>
+          <t>1665-658-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8588.98</v>
+        <v>9080.620000000001</v>
       </c>
     </row>
     <row r="195">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2940-158-CM25</t>
+          <t>1663-1227-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13144,17 +13144,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.210.201-0</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PABLO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6477.58</v>
+        <v>51983.7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1663-1227-CM25</t>
+          <t>2940-158-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13209,17 +13209,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>69.210.201-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>51983.7</v>
+        <v>6477.58</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1388974-200-CM25</t>
+          <t>1079639-751-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>71.146.000-4</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>15300.45</v>
+        <v>56484.57</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1079639-751-CM25</t>
+          <t>2887-180-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13339,17 +13339,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>56484.57</v>
+        <v>7231.05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2887-180-CM25</t>
+          <t>1388974-200-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>71.146.000-4</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>7231.05</v>
+        <v>15300.45</v>
       </c>
     </row>
     <row r="201">
@@ -13709,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>620279-144-CM25</t>
+          <t>1514-16050-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5662.98</v>
+        <v>52917.98</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1514-16050-CM25</t>
+          <t>620279-144-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>52917.98</v>
+        <v>5662.98</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>545598-591-CM25</t>
+          <t>2140-1335-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13859,17 +13859,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13898,7 +13898,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>38117.63</v>
+        <v>334.53</v>
       </c>
     </row>
     <row r="208">
@@ -13969,7 +13969,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2140-1334-CM25</t>
+          <t>545598-591-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>9648.48</v>
+        <v>38117.63</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2140-1335-CM25</t>
+          <t>2140-1334-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>334.53</v>
+        <v>9648.48</v>
       </c>
     </row>
     <row r="211">
@@ -14229,7 +14229,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1665-751-CM25</t>
+          <t>2139-4720-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>9124.059999999999</v>
+        <v>7703.58</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2139-4720-CM25</t>
+          <t>1665-751-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14314,12 +14314,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>7703.58</v>
+        <v>9124.059999999999</v>
       </c>
     </row>
     <row r="215">
@@ -15464,7 +15464,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1514-16578-CM25</t>
+          <t>2136-840-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15489,12 +15489,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.270-9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15523,7 +15523,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>35435.91</v>
+        <v>3683.38</v>
       </c>
     </row>
     <row r="233">
@@ -15594,7 +15594,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2136-840-CM25</t>
+          <t>1514-16578-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15619,12 +15619,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.602.270-9</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3683.38</v>
+        <v>35435.91</v>
       </c>
     </row>
     <row r="235">
@@ -15724,7 +15724,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3481-164-CM25</t>
+          <t>2140-1454-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3143.44</v>
+        <v>298.63</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2140-1453-CM25</t>
+          <t>2137-914-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>11085.01</v>
+        <v>12707.34</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2140-1454-CM25</t>
+          <t>2140-1453-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>298.63</v>
+        <v>11085.01</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2137-914-CM25</t>
+          <t>3481-164-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>12707.34</v>
+        <v>3143.44</v>
       </c>
     </row>
     <row r="240">
@@ -16049,7 +16049,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1079639-881-CM25</t>
+          <t>2139-4797-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>436.48</v>
+        <v>8511.370000000001</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2139-4797-CM25</t>
+          <t>1079639-881-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16139,12 +16139,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>8511.370000000001</v>
+        <v>436.48</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5413-1171-CM25</t>
+          <t>1079639-884-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2579.85</v>
+        <v>7446.63</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1079639-884-CM25</t>
+          <t>5413-1171-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>7446.63</v>
+        <v>2579.85</v>
       </c>
     </row>
     <row r="245">
@@ -16504,7 +16504,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3481-176-CM25</t>
+          <t>1057532-5385-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>211.92</v>
+        <v>376.52</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1057532-5385-CM25</t>
+          <t>3481-176-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16594,12 +16594,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>376.52</v>
+        <v>211.92</v>
       </c>
     </row>
     <row r="250">
@@ -17284,7 +17284,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>3481-185-CM25</t>
+          <t>3481-180-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>14635.02</v>
+        <v>1058.06</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2297-1581-CM25</t>
+          <t>3481-185-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17369,17 +17369,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1199.93</v>
+        <v>14635.02</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3481-180-CM25</t>
+          <t>2297-1581-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17434,17 +17434,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,7 +17473,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1058.06</v>
+        <v>1199.93</v>
       </c>
     </row>
     <row r="263">
@@ -17739,7 +17739,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1514-17015-CM25</t>
+          <t>1661-631-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>40611.16</v>
+        <v>16750.86</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1665-912-CM25</t>
+          <t>1514-17015-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17824,17 +17824,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>9952.700000000001</v>
+        <v>40611.16</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1661-631-CM25</t>
+          <t>1665-912-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17889,12 +17889,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>16750.86</v>
+        <v>9952.700000000001</v>
       </c>
     </row>
     <row r="270">
@@ -18454,7 +18454,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2660-69-CM25</t>
+          <t>1079639-1002-CM25</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18474,17 +18474,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>10402.01</v>
+        <v>63499.82</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1079639-1002-CM25</t>
+          <t>1079639-1056-CM25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>63499.82</v>
+        <v>2680.8</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1079639-1056-CM25</t>
+          <t>1079639-1058-CM25</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2680.8</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1079639-1058-CM25</t>
+          <t>2660-69-CM25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18669,17 +18669,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>100.26</v>
+        <v>10402.01</v>
       </c>
     </row>
     <row r="282">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1079639-1090-CM25</t>
+          <t>1079639-1074-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>158.61</v>
+        <v>939.48</v>
       </c>
     </row>
     <row r="285">
@@ -18974,7 +18974,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1079639-1074-CM25</t>
+          <t>1079639-1090-CM25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>939.48</v>
+        <v>158.61</v>
       </c>
     </row>
     <row r="287">
@@ -19169,7 +19169,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1079639-1065-CM25</t>
+          <t>1079639-1072-CM25</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>292.83</v>
+        <v>719.86</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1079639-1072-CM25</t>
+          <t>1079639-1065-CM25</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19293,7 +19293,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>719.86</v>
+        <v>292.83</v>
       </c>
     </row>
     <row r="291">
@@ -19494,7 +19494,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1079639-1075-CM25</t>
+          <t>1079639-1085-CM25</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>440.46</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="295">
@@ -19689,7 +19689,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1079639-1085-CM25</t>
+          <t>3481-190-CM25</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>244.7</v>
+        <v>15768.83</v>
       </c>
     </row>
     <row r="298">
@@ -19819,7 +19819,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3481-190-CM25</t>
+          <t>1079639-1075-CM25</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>15768.83</v>
+        <v>440.46</v>
       </c>
     </row>
     <row r="300">
@@ -22224,7 +22224,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1661-5-CM26</t>
+          <t>1514-115-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22283,13 +22283,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>15551.41</v>
+        <v>29620.97</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1514-115-CM26</t>
+          <t>1661-5-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>29620.97</v>
+        <v>15551.41</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2139-22-CM26</t>
+          <t>1057531-6-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,13 +22413,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>7580.57</v>
+        <v>14516.38</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1057531-6-CM26</t>
+          <t>2139-22-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22478,7 +22478,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>14516.38</v>
+        <v>7580.57</v>
       </c>
     </row>
     <row r="340">
@@ -23329,7 +23329,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1057536-375-CM26</t>
+          <t>1057532-207-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23354,12 +23354,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2810.23</v>
+        <v>1197.72</v>
       </c>
     </row>
     <row r="354">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2140-111-CM26</t>
+          <t>1057536-375-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23484,7 +23484,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>12217.38</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1057532-207-CM26</t>
+          <t>2140-111-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,13 +23583,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1197.72</v>
+        <v>12217.38</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>620279-15-CM26</t>
+          <t>2137-117-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23614,12 +23614,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>27683.57</v>
+        <v>15382.2</v>
       </c>
     </row>
     <row r="358">
@@ -23719,7 +23719,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2137-117-CM26</t>
+          <t>620279-15-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23744,12 +23744,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>15382.2</v>
+        <v>27683.57</v>
       </c>
     </row>
     <row r="360">
@@ -23849,7 +23849,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2139-171-CM26</t>
+          <t>1665-9865-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,7 +23874,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -23908,13 +23908,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>9498.9</v>
+        <v>8746.379999999999</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1665-9865-CM26</t>
+          <t>2139-171-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -23973,7 +23973,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>8746.379999999999</v>
+        <v>9498.9</v>
       </c>
     </row>
     <row r="363">
@@ -24109,7 +24109,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3481-22-CM26</t>
+          <t>1079639-81-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24134,12 +24134,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24168,13 +24168,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>4607.02</v>
+        <v>70203.98</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1079639-81-CM26</t>
+          <t>3481-22-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>70203.98</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="367">
@@ -24564,7 +24564,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>752-52-CM26</t>
+          <t>1057531-99-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24589,12 +24589,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24623,13 +24623,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3853.63</v>
+        <v>11933.69</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1057531-99-CM26</t>
+          <t>752-52-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24654,12 +24654,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24688,13 +24688,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>11933.69</v>
+        <v>3853.63</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1661-159-CM26</t>
+          <t>2140-190-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24719,7 +24719,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -24753,13 +24753,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>16639.2</v>
+        <v>12303.68</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2140-190-CM26</t>
+          <t>1661-159-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -24818,7 +24818,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>12303.68</v>
+        <v>16639.2</v>
       </c>
     </row>
     <row r="376">
@@ -24954,7 +24954,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1661-163-CM26</t>
+          <t>4443-16-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -25013,13 +25013,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>336.77</v>
+        <v>1128.05</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>4443-16-CM26</t>
+          <t>1661-163-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -25044,12 +25044,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -25078,7 +25078,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1128.05</v>
+        <v>336.77</v>
       </c>
     </row>
     <row r="380">
@@ -25409,7 +25409,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1057531-128-CM26</t>
+          <t>3480-36-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.101.471-6</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25468,13 +25468,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>12011.88</v>
+        <v>1634.71</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>3480-36-CM26</t>
+          <t>1057531-128-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.101.471-6</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1634.71</v>
+        <v>12011.88</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1079639-159-CM26</t>
+          <t>1079639-160-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25598,13 +25598,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>42721.57</v>
+        <v>37260.65</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1079639-160-CM26</t>
+          <t>1079639-159-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25663,7 +25663,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>37260.65</v>
+        <v>42721.57</v>
       </c>
     </row>
     <row r="389">
@@ -25734,7 +25734,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3481-37-CM26</t>
+          <t>1503362-43-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1610.19</v>
+        <v>1094.93</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1503362-42-CM26</t>
+          <t>3481-37-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25824,12 +25824,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25858,13 +25858,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>4301.39</v>
+        <v>1610.19</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1503362-43-CM26</t>
+          <t>1503362-42-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25923,7 +25923,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1094.93</v>
+        <v>4301.39</v>
       </c>
     </row>
     <row r="393">
@@ -26254,7 +26254,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>3443-280-CM26</t>
+          <t>1079639-273-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26274,17 +26274,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,13 +26313,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>14692.85</v>
+        <v>41482.95</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>3481-41-CM26</t>
+          <t>3443-280-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26339,17 +26339,17 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,13 +26378,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3335.6</v>
+        <v>14692.85</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1079639-273-CM26</t>
+          <t>3481-41-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26409,12 +26409,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26443,7 +26443,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>41482.95</v>
+        <v>3335.6</v>
       </c>
     </row>
     <row r="401">
@@ -26839,7 +26839,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1479-47-CM26</t>
+          <t>1479-46-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26898,13 +26898,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>402.2</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1479-46-CM26</t>
+          <t>1479-47-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26963,7 +26963,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>134.07</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="409">
@@ -27229,7 +27229,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2140-396-CM26</t>
+          <t>1665-10041-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,7 +27254,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -27288,13 +27288,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>11511.55</v>
+        <v>9901.030000000001</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1665-10041-CM26</t>
+          <t>2140-396-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>9901.030000000001</v>
+        <v>11511.55</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1079639-413-CM26</t>
+          <t>1079639-415-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>43956.67</v>
+        <v>18849.88</v>
       </c>
     </row>
     <row r="416">
@@ -27489,7 +27489,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1079639-415-CM26</t>
+          <t>1079639-413-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>18849.88</v>
+        <v>43956.67</v>
       </c>
     </row>
     <row r="418">
@@ -27749,7 +27749,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>853-99-CM26</t>
+          <t>707425-93-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>50158.71</v>
+        <v>5287.37</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>853-100-CM26</t>
+          <t>853-99-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27873,13 +27873,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>5202.5</v>
+        <v>50158.71</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>707425-93-CM26</t>
+          <t>853-100-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27904,12 +27904,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>5287.37</v>
+        <v>5202.5</v>
       </c>
     </row>
     <row r="424">
@@ -28334,7 +28334,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>584146-226-CM26</t>
+          <t>5110-197-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>632.1900000000001</v>
+        <v>652.67</v>
       </c>
     </row>
     <row r="431">
@@ -28464,7 +28464,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5110-197-CM26</t>
+          <t>584146-226-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>652.67</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="433">
@@ -29244,7 +29244,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1079639-556-CM26</t>
+          <t>1079639-557-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29303,13 +29303,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>26992.25</v>
+        <v>18695.93</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1079639-557-CM26</t>
+          <t>1079639-556-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -29368,7 +29368,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>18695.93</v>
+        <v>26992.25</v>
       </c>
     </row>
     <row r="446">
@@ -29504,7 +29504,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>507428-683-CM26</t>
+          <t>707425-120-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29524,17 +29524,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>31879.94</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>707425-120-CM26</t>
+          <t>507428-683-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29589,17 +29589,17 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29628,7 +29628,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>108.3</v>
+        <v>31879.94</v>
       </c>
     </row>
     <row r="450">
@@ -30024,7 +30024,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2139-583-CM26</t>
+          <t>1079639-606-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -30049,12 +30049,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -30083,13 +30083,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>9333.940000000001</v>
+        <v>42241.38</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1079639-606-CM26</t>
+          <t>2139-583-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30114,12 +30114,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -30148,7 +30148,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>42241.38</v>
+        <v>9333.940000000001</v>
       </c>
     </row>
     <row r="458">
@@ -30609,7 +30609,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>507428-772-CM26</t>
+          <t>2324-991-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30634,12 +30634,12 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -30649,17 +30649,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -30668,13 +30668,13 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>31212.51</v>
+        <v>1512.85</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2324-991-CM26</t>
+          <t>507428-772-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30699,12 +30699,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -30714,17 +30714,17 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -30733,7 +30733,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1512.85</v>
+        <v>31212.51</v>
       </c>
     </row>
     <row r="467">
@@ -31194,7 +31194,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1661-509-CM26</t>
+          <t>2140-722-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -31253,13 +31253,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>257.22</v>
+        <v>11741.87</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2140-722-CM26</t>
+          <t>1661-509-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>11741.87</v>
+        <v>257.22</v>
       </c>
     </row>
     <row r="476">
@@ -32689,7 +32689,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2139-764-CM26</t>
+          <t>1079639-744-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>8246.49</v>
+        <v>41635.25</v>
       </c>
     </row>
     <row r="498">
@@ -32819,7 +32819,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2140-813-CM26</t>
+          <t>1079639-745-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32839,17 +32839,17 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -32878,13 +32878,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>11716.36</v>
+        <v>26376.08</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1079639-746-CM26</t>
+          <t>2139-764-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32909,12 +32909,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -32943,13 +32943,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>18269.14</v>
+        <v>8246.49</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1079639-745-CM26</t>
+          <t>2140-813-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32974,12 +32974,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -33008,13 +33008,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>26376.08</v>
+        <v>11716.36</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1079639-744-CM26</t>
+          <t>1079639-746-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -33073,7 +33073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>41635.25</v>
+        <v>18269.14</v>
       </c>
     </row>
     <row r="503">
@@ -33294,7 +33294,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -33339,7 +33339,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1079639-764-CM26</t>
+          <t>2137-797-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33364,12 +33364,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>348.95</v>
+        <v>14751.07</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2048-2643-CM26</t>
+          <t>1079639-764-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33424,17 +33424,17 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -33463,13 +33463,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>13197.4</v>
+        <v>348.95</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2137-797-CM26</t>
+          <t>2048-2643-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33494,7 +33494,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -33528,7 +33528,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>14751.07</v>
+        <v>13197.4</v>
       </c>
     </row>
     <row r="510">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -33944,7 +33944,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -34009,7 +34009,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -34119,7 +34119,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>4132-207-CM26</t>
+          <t>2138-417-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -34139,17 +34139,17 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -34178,13 +34178,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>29898.34</v>
+        <v>18562.44</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2138-417-CM26</t>
+          <t>4132-207-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -34209,12 +34209,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -34243,13 +34243,13 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>18562.44</v>
+        <v>29898.34</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2324-1377-CM26</t>
+          <t>1057534-1309-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -34274,12 +34274,12 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -34289,17 +34289,17 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -34308,13 +34308,13 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>36044.76</v>
+        <v>21639.22</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1057534-1309-CM26</t>
+          <t>2324-1377-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -34334,46 +34334,1411 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="n">
+        <v>36044.76</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>1057531-446-CM26</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>61.602.262-8</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M523" s="2" t="n">
+        <v>13302.64</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2059-516-CM26</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>61.607.602-7</t>
-        </is>
-      </c>
-      <c r="G522" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
-        </is>
-      </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="I522" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J522" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K522" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L522" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M522" s="2" t="n">
-        <v>21639.22</v>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>61.602.261-k</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO OCTAY</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="n">
+        <v>14245.83</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>1661-658-CM26</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>61.602.268-7</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M525" s="2" t="n">
+        <v>16694.56</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>1057727-44-CM26</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M526" s="2" t="n">
+        <v>180.57</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2048-2956-CM26</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>61.975.800-5</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M527" s="2" t="n">
+        <v>55862.32</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>707425-196-CM26</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="n">
+        <v>5102.85</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2140-920-CM26</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>61.602.274-1</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M529" s="2" t="n">
+        <v>10965.16</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2140-921-CM26</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>61.602.274-1</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="n">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2324-1423-CM26</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M531" s="2" t="n">
+        <v>35665.13</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2048-2995-CM26</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>61.975.800-5</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M532" s="2" t="n">
+        <v>13521.73</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2137-909-CM26</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>61.602.278-4</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M533" s="2" t="n">
+        <v>12966.77</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2139-866-CM26</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>61.602.312-8</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M534" s="2" t="n">
+        <v>7535.94</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>1079639-828-CM26</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M535" s="2" t="n">
+        <v>5258.28</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>1079639-829-CM26</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M536" s="2" t="n">
+        <v>39004.2</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>1079639-830-CM26</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M537" s="2" t="n">
+        <v>24770.31</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>1079639-831-CM26</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M538" s="2" t="n">
+        <v>17373.41</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1665-10399-CM26</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>61.602.311-k</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M539" s="2" t="n">
+        <v>9388.65</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1661-665-CM26</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>61.602.268-7</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="n">
+        <v>47.66</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>3481-137-CM26</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>61.101.015-K</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M541" s="2" t="n">
+        <v>715.34</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>1079639-847-CM26</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="n">
+        <v>358.49</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>3481-139-CM26</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>61.101.015-K</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M543" s="2" t="n">
+        <v>5109.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M542"/>
+  <dimension ref="A1:M543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23264,7 +23264,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2140-111-CM26</t>
+          <t>1057532-207-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23323,13 +23323,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>12217.38</v>
+        <v>1197.72</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1057536-376-CM26</t>
+          <t>2140-111-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2810.23</v>
+        <v>12217.38</v>
       </c>
     </row>
     <row r="354">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1057532-207-CM26</t>
+          <t>1057536-376-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1197.72</v>
+        <v>2810.23</v>
       </c>
     </row>
     <row r="356">
@@ -23784,7 +23784,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1665-9865-CM26</t>
+          <t>2138-106-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>8746.379999999999</v>
+        <v>17371.16</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2139-171-CM26</t>
+          <t>1665-9865-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,7 +23874,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -23908,13 +23908,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>9498.9</v>
+        <v>8746.379999999999</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2138-106-CM26</t>
+          <t>2139-171-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23939,12 +23939,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23973,7 +23973,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>17371.16</v>
+        <v>9498.9</v>
       </c>
     </row>
     <row r="363">
@@ -25344,7 +25344,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>3480-36-CM26</t>
+          <t>1057531-128-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25369,12 +25369,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.101.471-6</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1634.71</v>
+        <v>12011.88</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1057531-128-CM26</t>
+          <t>3480-36-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.101.471-6</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>12011.88</v>
+        <v>1634.71</v>
       </c>
     </row>
     <row r="386">
@@ -25539,7 +25539,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1079639-193-CM26</t>
+          <t>1079639-160-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25598,13 +25598,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>6572.23</v>
+        <v>37260.65</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1079639-160-CM26</t>
+          <t>1079639-193-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25663,7 +25663,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>37260.65</v>
+        <v>6572.23</v>
       </c>
     </row>
     <row r="389">
@@ -25734,7 +25734,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1503362-42-CM26</t>
+          <t>3481-37-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>4301.39</v>
+        <v>1610.19</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>3481-37-CM26</t>
+          <t>1503362-42-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25824,12 +25824,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1610.19</v>
+        <v>4301.39</v>
       </c>
     </row>
     <row r="392">
@@ -25994,7 +25994,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>3443-280-CM26</t>
+          <t>2139-328-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26014,17 +26014,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26053,13 +26053,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>14692.85</v>
+        <v>8441.719999999999</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2139-328-CM26</t>
+          <t>1079639-276-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26084,12 +26084,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26118,13 +26118,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>8441.719999999999</v>
+        <v>18252.37</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1079639-276-CM26</t>
+          <t>1079639-275-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26183,13 +26183,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>18252.37</v>
+        <v>26351.86</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1079639-275-CM26</t>
+          <t>1079639-273-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26248,13 +26248,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>26351.86</v>
+        <v>41482.95</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>3481-41-CM26</t>
+          <t>3443-280-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26274,17 +26274,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,13 +26313,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>3335.6</v>
+        <v>14692.85</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1079639-273-CM26</t>
+          <t>3481-41-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26344,12 +26344,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,13 +26378,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>41482.95</v>
+        <v>3335.6</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1665-9977-CM26</t>
+          <t>2137-275-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26409,12 +26409,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26443,13 +26443,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>10217.36</v>
+        <v>15441.72</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2137-275-CM26</t>
+          <t>1665-9977-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26474,12 +26474,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>15441.72</v>
+        <v>10217.36</v>
       </c>
     </row>
     <row r="402">
@@ -26774,7 +26774,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1479-47-CM26</t>
+          <t>1479-46-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26833,13 +26833,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>402.2</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1479-46-CM26</t>
+          <t>1479-47-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>134.07</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="408">
@@ -27164,7 +27164,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1665-10041-CM26</t>
+          <t>2140-396-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,7 +27189,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>9901.030000000001</v>
+        <v>11511.55</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2140-396-CM26</t>
+          <t>1665-10041-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,7 +27254,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>11511.55</v>
+        <v>9901.030000000001</v>
       </c>
     </row>
     <row r="414">
@@ -27749,7 +27749,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>853-99-CM26</t>
+          <t>853-100-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>50158.71</v>
+        <v>5202.5</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>853-100-CM26</t>
+          <t>853-99-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27873,7 +27873,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>5202.5</v>
+        <v>50158.71</v>
       </c>
     </row>
     <row r="423">
@@ -28334,7 +28334,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1057534-666-CM26</t>
+          <t>584146-226-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28354,17 +28354,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28393,13 +28393,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>22399.18</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>584146-226-CM26</t>
+          <t>1057534-666-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28419,17 +28419,17 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -28458,7 +28458,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>632.1900000000001</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="432">
@@ -29114,7 +29114,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1079639-555-CM26</t>
+          <t>1079639-556-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -29173,13 +29173,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>42615.47</v>
+        <v>26992.25</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1079639-556-CM26</t>
+          <t>1079639-557-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -29238,13 +29238,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>26992.25</v>
+        <v>18695.93</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1079639-557-CM26</t>
+          <t>1079639-555-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29303,7 +29303,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>18695.93</v>
+        <v>42615.47</v>
       </c>
     </row>
     <row r="445">
@@ -29569,7 +29569,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1057531-302-CM26</t>
+          <t>2140-592-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29594,12 +29594,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29628,13 +29628,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>12824.49</v>
+        <v>11945.88</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2140-591-CM26</t>
+          <t>1661-416-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -29693,13 +29693,13 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>219.94</v>
+        <v>18317.85</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2140-592-CM26</t>
+          <t>1057531-302-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29724,12 +29724,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -29758,13 +29758,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>11945.88</v>
+        <v>12824.49</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1661-416-CM26</t>
+          <t>2140-591-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -29823,7 +29823,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>18317.85</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="453">
@@ -31194,7 +31194,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1661-509-CM26</t>
+          <t>2140-723-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -31253,13 +31253,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>257.22</v>
+        <v>282.94</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2140-723-CM26</t>
+          <t>1661-509-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>282.94</v>
+        <v>257.22</v>
       </c>
     </row>
     <row r="476">
@@ -31714,7 +31714,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1079639-698-CM26</t>
+          <t>1079639-695-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>38690.27</v>
+        <v>26482.07</v>
       </c>
     </row>
     <row r="483">
@@ -31844,7 +31844,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>1079639-695-CM26</t>
+          <t>1079639-698-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31903,7 +31903,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>26482.07</v>
+        <v>38690.27</v>
       </c>
     </row>
     <row r="485">
@@ -32104,7 +32104,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>4132-198-CM26</t>
+          <t>2324-1213-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32129,12 +32129,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -32144,12 +32144,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
@@ -32163,13 +32163,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>33704.59</v>
+        <v>37497.32</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2324-1213-CM26</t>
+          <t>4132-198-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32194,12 +32194,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -32209,12 +32209,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>37497.32</v>
+        <v>33704.59</v>
       </c>
     </row>
     <row r="490">
@@ -32299,7 +32299,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1057531-391-CM26</t>
+          <t>3443-679-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32319,17 +32319,17 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -32358,13 +32358,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>16069.08</v>
+        <v>1734.26</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>3443-679-CM26</t>
+          <t>1057531-391-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32384,17 +32384,17 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -32423,7 +32423,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>1734.26</v>
+        <v>16069.08</v>
       </c>
     </row>
     <row r="493">
@@ -32494,7 +32494,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1057533-401-CM26</t>
+          <t>1057533-400-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -32553,13 +32553,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>314.83</v>
+        <v>524.73</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1057533-400-CM26</t>
+          <t>1057533-401-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>524.73</v>
+        <v>314.83</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1079639-744-CM26</t>
+          <t>2140-813-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32649,12 +32649,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32683,13 +32683,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>41635.25</v>
+        <v>11716.36</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1079639-751-CM26</t>
+          <t>1079639-744-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32748,13 +32748,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>11333.63</v>
+        <v>41635.25</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1079639-745-CM26</t>
+          <t>1079639-751-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32813,7 +32813,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>26376.08</v>
+        <v>11333.63</v>
       </c>
     </row>
     <row r="499">
@@ -32884,7 +32884,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2140-813-CM26</t>
+          <t>1079639-746-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32909,12 +32909,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -32943,13 +32943,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>11716.36</v>
+        <v>18269.14</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1079639-746-CM26</t>
+          <t>1079639-745-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -33008,7 +33008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>18269.14</v>
+        <v>26376.08</v>
       </c>
     </row>
     <row r="502">
@@ -33274,7 +33274,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2137-797-CM26</t>
+          <t>2048-2643-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -33333,7 +33333,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>14751.07</v>
+        <v>13197.4</v>
       </c>
     </row>
     <row r="507">
@@ -33404,7 +33404,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2048-2643-CM26</t>
+          <t>2137-797-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33429,7 +33429,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -33463,13 +33463,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>13197.4</v>
+        <v>14751.07</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>608897-254-CM26</t>
+          <t>545598-813-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33494,12 +33494,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -33509,12 +33509,12 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
@@ -33528,13 +33528,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>2424.99</v>
+        <v>125.43</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>545598-813-CM26</t>
+          <t>608897-254-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33559,12 +33559,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33574,12 +33574,12 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -33593,7 +33593,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>125.43</v>
+        <v>2424.99</v>
       </c>
     </row>
     <row r="511">
@@ -34444,7 +34444,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1661-658-CM26</t>
+          <t>1057727-44-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34484,12 +34484,12 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>16694.56</v>
+        <v>180.57</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1057727-44-CM26</t>
+          <t>2048-2956-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34529,17 +34529,17 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -34549,12 +34549,12 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>180.57</v>
+        <v>55862.32</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2048-2956-CM26</t>
+          <t>1661-658-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34594,17 +34594,17 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -34633,7 +34633,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>55862.32</v>
+        <v>16694.56</v>
       </c>
     </row>
     <row r="527">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -35549,7 +35549,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1079639-847-CM26</t>
+          <t>3481-139-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35574,12 +35574,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -35589,12 +35589,12 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
@@ -35608,13 +35608,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>358.49</v>
+        <v>5109.55</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>3481-139-CM26</t>
+          <t>1079639-847-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -35634,46 +35634,111 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="n">
+        <v>358.49</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>1057533-498-CM26</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>61.101.015-K</t>
-        </is>
-      </c>
-      <c r="G542" t="inlineStr">
-        <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
-        </is>
-      </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
-        </is>
-      </c>
-      <c r="J542" t="inlineStr">
-        <is>
-          <t>96.556.930-8</t>
-        </is>
-      </c>
-      <c r="K542" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M542" s="2" t="n">
-        <v>5109.55</v>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>61.980.080-K</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>HOSPITAL DEL PERPETUO SOCORRO DE QUILACAHUIN</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M543" s="2" t="n">
+        <v>403.74</v>
       </c>
     </row>
   </sheetData>
